--- a/output/stock_quant_scores/KMI_info.xlsx
+++ b/output/stock_quant_scores/KMI_info.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FV2"/>
+  <dimension ref="A1:FZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1086,230 +1086,250 @@
       </c>
       <c r="EC1" s="1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketTime</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EK1" s="1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="EL1" s="1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="EM1" s="1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="EK1" s="1" t="inlineStr">
+      <c r="EN1" s="1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
+      <c r="EO1" s="1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="EM1" s="1" t="inlineStr">
+      <c r="EP1" s="1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>averageAnalystRating</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="FI1" s="1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="FJ1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="FK1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketPrice</t>
+        </is>
+      </c>
+      <c r="FL1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChange</t>
+        </is>
+      </c>
+      <c r="FM1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="FN1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="FO1" s="1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="FP1" s="1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="FQ1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="FR1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="EO1" s="1" t="inlineStr">
+      <c r="FS1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="EP1" s="1" t="inlineStr">
+      <c r="FT1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="EQ1" s="1" t="inlineStr">
+      <c r="FU1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="ER1" s="1" t="inlineStr">
+      <c r="FV1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="ES1" s="1" t="inlineStr">
+      <c r="FW1" s="1" t="inlineStr">
         <is>
           <t>dividendDate</t>
         </is>
       </c>
-      <c r="ET1" s="1" t="inlineStr">
+      <c r="FX1" s="1" t="inlineStr">
         <is>
           <t>earningsTimestamp</t>
         </is>
       </c>
-      <c r="EU1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EV1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="EX1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="FA1" s="1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="FD1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="FE1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="FF1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="FG1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="FH1" s="1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="FI1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="FJ1" s="1" t="inlineStr">
-        <is>
-          <t>averageAnalystRating</t>
-        </is>
-      </c>
-      <c r="FK1" s="1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="FL1" s="1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="FM1" s="1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="FN1" s="1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="FO1" s="1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="FP1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="FQ1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="FR1" s="1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="FS1" s="1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="FT1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="FU1" s="1" t="inlineStr">
+      <c r="FY1" s="1" t="inlineStr">
         <is>
           <t>displayName</t>
         </is>
       </c>
-      <c r="FV1" s="1" t="inlineStr">
+      <c r="FZ1" s="1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -1399,7 +1419,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Richard D. Kinder', 'age': 79, 'title': 'Executive Chairman of the Board', 'yearBorn': 1945, 'fiscalYear': 2024, 'totalPay': 1, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Kimberly Allen Dang', 'age': 54, 'title': 'CEO &amp; Director', 'yearBorn': 1970, 'fiscalYear': 2024, 'totalPay': 517250, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. David Patrick Michels', 'age': 45, 'title': 'VP &amp; CFO', 'yearBorn': 1979, 'fiscalYear': 2024, 'totalPay': 1252250, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. John W. Schlosser', 'age': 61, 'title': 'VP &amp; President of Terminals', 'yearBorn': 1963, 'fiscalYear': 2024, 'totalPay': 1270118, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Sital K. Mody', 'age': 53, 'title': 'VP &amp; President of Natural Gas Pipelines', 'yearBorn': 1971, 'fiscalYear': 2024, 'totalPay': 1567250, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Thomas A. Martin', 'age': 62, 'title': 'President', 'yearBorn': 1962, 'fiscalYear': 2024, 'totalPay': 1739577, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. James E. Holland', 'age': 61, 'title': 'VP &amp; COO', 'yearBorn': 1963, 'fiscalYear': 2024, 'totalPay': 1174577, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Mark  Huse', 'title': 'VP &amp; Chief Information Officer', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Michael J. Pitta', 'age': 50, 'title': 'VP &amp; Chief Administrative Officer', 'yearBorn': 1974, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Catherine B. Callaway James J.D.', 'age': 59, 'title': 'VP &amp; General Counsel', 'yearBorn': 1965, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Richard D. Kinder', 'age': 79, 'title': 'Executive Chairman of the Board', 'yearBorn': 1945, 'fiscalYear': 2024, 'totalPay': 1, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Kimberly Allen Dang', 'age': 54, 'title': 'CEO &amp; Director', 'yearBorn': 1970, 'fiscalYear': 2024, 'totalPay': 517250, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. David Patrick Michels', 'age': 45, 'title': 'VP &amp; CFO', 'yearBorn': 1979, 'fiscalYear': 2024, 'totalPay': 1252250, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. John W. Schlosser', 'age': 61, 'title': 'VP &amp; President of Terminals', 'yearBorn': 1963, 'fiscalYear': 2024, 'totalPay': 1270118, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Dax A. Sanders C.P.A.', 'age': 49, 'title': 'Executive Vice President', 'yearBorn': 1975, 'fiscalYear': 2024, 'totalPay': 1242250, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Sital K. Mody', 'age': 53, 'title': 'VP &amp; President of Natural Gas Pipelines', 'yearBorn': 1971, 'fiscalYear': 2024, 'totalPay': 1567250, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Thomas A. Martin', 'age': 62, 'title': 'President', 'yearBorn': 1962, 'fiscalYear': 2024, 'totalPay': 1739577, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. James E. Holland', 'age': 61, 'title': 'VP &amp; COO', 'yearBorn': 1963, 'fiscalYear': 2024, 'totalPay': 1174577, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Mark  Huse', 'title': 'VP &amp; Chief Information Officer', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Michael J. Pitta', 'age': 50, 'title': 'VP &amp; Chief Administrative Officer', 'yearBorn': 1974, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="S2" t="n">
@@ -1440,34 +1460,34 @@
         <v>2</v>
       </c>
       <c r="AD2" t="n">
-        <v>27.47</v>
+        <v>27.93</v>
       </c>
       <c r="AE2" t="n">
-        <v>27.63</v>
+        <v>28.18</v>
       </c>
       <c r="AF2" t="n">
-        <v>27.61</v>
+        <v>28.03</v>
       </c>
       <c r="AG2" t="n">
+        <v>28.51</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>28.18</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>28.03</v>
       </c>
-      <c r="AH2" t="n">
-        <v>27.47</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>27.63</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>27.61</v>
-      </c>
       <c r="AK2" t="n">
-        <v>28.03</v>
+        <v>28.51</v>
       </c>
       <c r="AL2" t="n">
         <v>1.17</v>
       </c>
       <c r="AM2" t="n">
-        <v>4.26</v>
+        <v>4.15</v>
       </c>
       <c r="AN2" t="n">
         <v>1753920000</v>
@@ -1482,43 +1502,43 @@
         <v>0.8179999999999999</v>
       </c>
       <c r="AR2" t="n">
-        <v>22.758196</v>
+        <v>23.12295</v>
       </c>
       <c r="AS2" t="n">
-        <v>22.035713</v>
+        <v>22.388887</v>
       </c>
       <c r="AT2" t="n">
-        <v>8372983</v>
+        <v>13768835</v>
       </c>
       <c r="AU2" t="n">
-        <v>8372983</v>
+        <v>13768835</v>
       </c>
       <c r="AV2" t="n">
-        <v>14398636</v>
+        <v>14376938</v>
       </c>
       <c r="AW2" t="n">
-        <v>11534670</v>
+        <v>12491350</v>
       </c>
       <c r="AX2" t="n">
-        <v>11534670</v>
+        <v>12491350</v>
       </c>
       <c r="AY2" t="n">
-        <v>27.84</v>
+        <v>28.21</v>
       </c>
       <c r="AZ2" t="n">
-        <v>27.85</v>
+        <v>28.22</v>
       </c>
       <c r="BA2" t="n">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="BB2" t="n">
-        <v>46</v>
+        <v>127</v>
       </c>
       <c r="BC2" t="n">
-        <v>61695987712</v>
+        <v>62684811264</v>
       </c>
       <c r="BD2" t="n">
-        <v>21.61</v>
+        <v>21.65</v>
       </c>
       <c r="BE2" t="n">
         <v>31.48</v>
@@ -1530,19 +1550,19 @@
         <v>9.42</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.8634846</v>
+        <v>3.925406</v>
       </c>
       <c r="BI2" t="n">
-        <v>27.1536</v>
+        <v>27.166</v>
       </c>
       <c r="BJ2" t="n">
-        <v>27.4374</v>
+        <v>27.44155</v>
       </c>
       <c r="BK2" t="n">
         <v>1.16</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.042227887</v>
+        <v>0.0415324</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
@@ -1553,7 +1573,7 @@
         <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>95075475456</v>
+        <v>96719806464</v>
       </c>
       <c r="BP2" t="n">
         <v>0.17058</v>
@@ -1565,31 +1585,31 @@
         <v>2222077616</v>
       </c>
       <c r="BS2" t="n">
-        <v>37333362</v>
+        <v>36981496</v>
       </c>
       <c r="BT2" t="n">
-        <v>39450255</v>
+        <v>35535055</v>
       </c>
       <c r="BU2" t="n">
-        <v>1753920000</v>
+        <v>1755216000</v>
       </c>
       <c r="BV2" t="n">
-        <v>1756425600</v>
+        <v>1757894400</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.0168</v>
+        <v>0.0166</v>
       </c>
       <c r="BX2" t="n">
         <v>0.12749</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.68471</v>
+        <v>0.68483</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.42</v>
+        <v>3.04</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.0222</v>
+        <v>0.022</v>
       </c>
       <c r="CB2" t="n">
         <v>2222077616</v>
@@ -1598,7 +1618,7 @@
         <v>13.847</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.0051274</v>
+        <v>2.0372643</v>
       </c>
       <c r="CE2" t="n">
         <v>1735603200</v>
@@ -1622,16 +1642,16 @@
         <v>1.26</v>
       </c>
       <c r="CL2" t="n">
-        <v>5.954</v>
+        <v>6.057</v>
       </c>
       <c r="CM2" t="n">
-        <v>14.146</v>
+        <v>14.391</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.24354911</v>
+        <v>0.27704847</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.16333759</v>
+        <v>0.1529237</v>
       </c>
       <c r="CP2" t="n">
         <v>0.293</v>
@@ -1645,7 +1665,7 @@
         </is>
       </c>
       <c r="CS2" t="n">
-        <v>27.765</v>
+        <v>28.21</v>
       </c>
       <c r="CT2" t="n">
         <v>38</v>
@@ -1767,172 +1787,184 @@
       </c>
       <c r="EB2" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="EC2" t="inlineStr">
         <is>
+          <t>Kinder Morgan, Inc.</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="ED2" t="n">
-        <v>1758740027</v>
-      </c>
       <c r="EE2" t="inlineStr">
         <is>
+          <t>Kinder Morgan, Inc.</t>
+        </is>
+      </c>
+      <c r="EF2" t="n">
+        <v>1758930825</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>1758916802</v>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
           <t>NYQ</t>
         </is>
       </c>
-      <c r="EF2" t="inlineStr">
+      <c r="EI2" t="inlineStr">
         <is>
           <t>finmb_34952431</t>
         </is>
       </c>
-      <c r="EG2" t="inlineStr">
+      <c r="EJ2" t="inlineStr">
         <is>
           <t>America/New_York</t>
         </is>
       </c>
-      <c r="EH2" t="inlineStr">
+      <c r="EK2" t="inlineStr">
         <is>
           <t>EDT</t>
         </is>
       </c>
-      <c r="EI2" t="n">
+      <c r="EL2" t="n">
         <v>-14400000</v>
       </c>
-      <c r="EJ2" t="inlineStr">
+      <c r="EM2" t="inlineStr">
         <is>
           <t>us_market</t>
         </is>
       </c>
-      <c r="EK2" t="b">
+      <c r="EN2" t="b">
         <v>0</v>
       </c>
-      <c r="EL2" t="n">
-        <v>1.0738991</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>27.765</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>0.28482178</v>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>21.61 - 31.48</t>
-        </is>
+      <c r="EO2" t="n">
+        <v>1.0025</v>
       </c>
       <c r="EP2" t="n">
-        <v>-3.7150002</v>
+        <v>28.21</v>
       </c>
       <c r="EQ2" t="n">
-        <v>-0.118011445</v>
+        <v>1761163200</v>
       </c>
       <c r="ER2" t="n">
-        <v>24.354912</v>
+        <v>1761163200</v>
       </c>
       <c r="ES2" t="n">
+        <v>1752697800</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>1752697800</v>
+      </c>
+      <c r="EU2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>1.28369</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>21.97571</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>1.0439987</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>0.038430344</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>0.7684498</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>0.028003149</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>15</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF2" t="inlineStr">
+        <is>
+          <t>1.9 - Buy</t>
+        </is>
+      </c>
+      <c r="FG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="FH2" t="b">
+        <v>1</v>
+      </c>
+      <c r="FI2" t="n">
+        <v>1297434600000</v>
+      </c>
+      <c r="FJ2" t="n">
+        <v>0.31903636</v>
+      </c>
+      <c r="FK2" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="FL2" t="n">
+        <v>0.09000015</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>0.279999</v>
+      </c>
+      <c r="FN2" t="inlineStr">
+        <is>
+          <t>28.03 - 28.51</t>
+        </is>
+      </c>
+      <c r="FO2" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="FP2" t="n">
+        <v>14376938</v>
+      </c>
+      <c r="FQ2" t="n">
+        <v>6.5599995</v>
+      </c>
+      <c r="FR2" t="n">
+        <v>0.3030023</v>
+      </c>
+      <c r="FS2" t="inlineStr">
+        <is>
+          <t>21.65 - 31.48</t>
+        </is>
+      </c>
+      <c r="FT2" t="n">
+        <v>-3.2700005</v>
+      </c>
+      <c r="FU2" t="n">
+        <v>-0.103875495</v>
+      </c>
+      <c r="FV2" t="n">
+        <v>27.704847</v>
+      </c>
+      <c r="FW2" t="n">
         <v>1755216000</v>
       </c>
-      <c r="ET2" t="n">
+      <c r="FX2" t="n">
         <v>1761163200</v>
       </c>
-      <c r="EU2" t="n">
-        <v>1761163200</v>
-      </c>
-      <c r="EV2" t="n">
-        <v>1761163200</v>
-      </c>
-      <c r="EW2" t="n">
-        <v>1752697800</v>
-      </c>
-      <c r="EX2" t="n">
-        <v>1752697800</v>
-      </c>
-      <c r="EY2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EZ2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="FA2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="FB2" t="n">
-        <v>1.28369</v>
-      </c>
-      <c r="FC2" t="n">
-        <v>21.629053</v>
-      </c>
-      <c r="FD2" t="n">
-        <v>0.6113987</v>
-      </c>
-      <c r="FE2" t="n">
-        <v>0.022516303</v>
-      </c>
-      <c r="FF2" t="n">
-        <v>0.32759857</v>
-      </c>
-      <c r="FG2" t="n">
-        <v>0.011939854</v>
-      </c>
-      <c r="FH2" t="n">
-        <v>15</v>
-      </c>
-      <c r="FI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="FJ2" t="inlineStr">
-        <is>
-          <t>1.9 - Buy</t>
-        </is>
-      </c>
-      <c r="FK2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FL2" t="inlineStr">
-        <is>
-          <t>Kinder Morgan, Inc.</t>
-        </is>
-      </c>
-      <c r="FM2" t="inlineStr">
-        <is>
-          <t>Kinder Morgan, Inc.</t>
-        </is>
-      </c>
-      <c r="FN2" t="b">
-        <v>1</v>
-      </c>
-      <c r="FO2" t="n">
-        <v>1297434600000</v>
-      </c>
-      <c r="FP2" t="n">
-        <v>0.29500008</v>
-      </c>
-      <c r="FQ2" t="inlineStr">
-        <is>
-          <t>27.61 - 28.03</t>
-        </is>
-      </c>
-      <c r="FR2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="FS2" t="n">
-        <v>14398636</v>
-      </c>
-      <c r="FT2" t="n">
-        <v>6.154999</v>
-      </c>
-      <c r="FU2" t="inlineStr">
+      <c r="FY2" t="inlineStr">
         <is>
           <t>Kinder Morgan</t>
         </is>
       </c>
-      <c r="FV2" t="n">
-        <v>2.0512</v>
+      <c r="FZ2" t="n">
+        <v>2.1065</v>
       </c>
     </row>
   </sheetData>
